--- a/passports/archivio_passport.xlsx
+++ b/passports/archivio_passport.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -67,6 +67,12 @@
   </si>
   <si>
     <t>Dato affidabile</t>
+  </si>
+  <si>
+    <t>file_base64</t>
+  </si>
+  <si>
+    <t>caption</t>
   </si>
 </sst>
 </file>
@@ -76,7 +82,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -94,13 +100,23 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color rgb="FF31333F"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -109,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -121,6 +137,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -450,7 +469,19 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>